--- a/excel/keywords.xlsx
+++ b/excel/keywords.xlsx
@@ -543,18 +543,18 @@
         <v>3570</v>
       </c>
       <c r="B3" t="n">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000089924300000649/0000899243-00-000649.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000089924302000927/0000899243-02-000927.txt</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>122</v>
+        <v>67</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -586,24 +586,24 @@
         <v>3570</v>
       </c>
       <c r="B4" t="n">
-        <v>2002</v>
+        <v>2007</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000089924303000668/0000899243-03-000668.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000119312508039317/d10k.htm</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>81</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -615,10 +615,10 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -629,24 +629,24 @@
         <v>3570</v>
       </c>
       <c r="B5" t="n">
-        <v>2008</v>
+        <v>2002</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000119312509040197/d10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000089924303000668/0000899243-03-000668.txt</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>81</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -672,24 +672,24 @@
         <v>3570</v>
       </c>
       <c r="B6" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000119312505046389/d10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000119312506051265/d10k.htm</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -701,10 +701,10 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -715,18 +715,18 @@
         <v>3570</v>
       </c>
       <c r="B7" t="n">
-        <v>2001</v>
+        <v>1999</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000089924302000927/0000899243-02-000927.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000089924300000649/0000899243-00-000649.txt</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>67</v>
+        <v>122</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -758,24 +758,24 @@
         <v>3570</v>
       </c>
       <c r="B8" t="n">
-        <v>2009</v>
+        <v>2004</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000000357010000005/form_10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000119312505046389/d10k.htm</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>66</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -784,13 +784,13 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -801,24 +801,24 @@
         <v>3570</v>
       </c>
       <c r="B9" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000119312506051265/d10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000119312507041208/d10k.htm</t>
         </is>
       </c>
       <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>23</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="n">
         <v>4</v>
-      </c>
-      <c r="E9" t="n">
-        <v>49</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>5</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -844,24 +844,24 @@
         <v>3570</v>
       </c>
       <c r="B10" t="n">
-        <v>2007</v>
+        <v>2010</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000119312508039317/d10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000000357011000026/cei201010k.htm</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -873,10 +873,10 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -887,24 +887,24 @@
         <v>3570</v>
       </c>
       <c r="B11" t="n">
-        <v>2006</v>
+        <v>2008</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000119312507041208/d10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000119312509040197/d10k.htm</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
         <v>2</v>
-      </c>
-      <c r="G11" t="n">
-        <v>4</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -930,11 +930,11 @@
         <v>3570</v>
       </c>
       <c r="B12" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000000357011000026/cei201010k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000000357010000005/form_10k.htm</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -947,7 +947,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -956,13 +956,13 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -973,24 +973,24 @@
         <v>3570</v>
       </c>
       <c r="B13" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000000357012000016/cei2011form10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000000357013000036/cei2012form10k.htm</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1005,7 +1005,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1016,18 +1016,18 @@
         <v>3570</v>
       </c>
       <c r="B14" t="n">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000000357014000031/cei2013form10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000000357012000016/cei2011form10k.htm</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1048,7 +1048,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1059,24 +1059,24 @@
         <v>3570</v>
       </c>
       <c r="B15" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000000357013000036/cei2012form10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000000357014000031/cei2013form10k.htm</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1091,7 +1091,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -1188,11 +1188,11 @@
         <v>3570</v>
       </c>
       <c r="B18" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000000357018000031/cei2017form10-k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000000357019000030/cei2018form10-k.htm</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1231,24 +1231,24 @@
         <v>3570</v>
       </c>
       <c r="B19" t="n">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000000357017000052/cei2016form10-k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000000357020000043/cei2019form10k.htm</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1257,13 +1257,13 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -1274,11 +1274,11 @@
         <v>3570</v>
       </c>
       <c r="B20" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000000357019000030/cei2018form10-k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000000357018000031/cei2017form10-k.htm</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1317,15 +1317,15 @@
         <v>3570</v>
       </c>
       <c r="B21" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000000357021000039/lng-20201231.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000000357022000024/lng-20211231.htm</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -1343,13 +1343,13 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -1360,15 +1360,15 @@
         <v>3570</v>
       </c>
       <c r="B22" t="n">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000000357022000024/lng-20211231.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000000357017000052/cei2016form10-k.htm</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -1377,7 +1377,7 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1386,13 +1386,13 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -1403,18 +1403,18 @@
         <v>3570</v>
       </c>
       <c r="B23" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000000357020000043/cei2019form10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000000357021000039/lng-20201231.htm</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1429,13 +1429,13 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -1443,27 +1443,27 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>3721</v>
+        <v>3662</v>
       </c>
       <c r="B24" t="n">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003721/000095015200002296/0000950152-00-002296.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003662/000095017099000775/0000950170-99-000775.txt</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -1489,24 +1489,24 @@
         <v>3662</v>
       </c>
       <c r="B25" t="n">
-        <v>1999</v>
+        <v>1997</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003662/000095017000000680/0000950170-00-000680.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003662/000095017098000413/0000950170-98-000413.txt</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1521,7 +1521,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -1529,27 +1529,27 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>3721</v>
+        <v>3662</v>
       </c>
       <c r="B26" t="n">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003721/000095015299002425/0000950152-99-002425.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003662/000095017000000680/0000950170-00-000680.txt</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1564,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -1572,27 +1572,27 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>3662</v>
+        <v>3721</v>
       </c>
       <c r="B27" t="n">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003662/000095017099000775/0000950170-99-000775.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003721/000095015298002155/0000950152-98-002155.txt</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1607,7 +1607,7 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -1615,27 +1615,27 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>3662</v>
+        <v>3721</v>
       </c>
       <c r="B28" t="n">
-        <v>1997</v>
+        <v>2000</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003662/000095017098000413/0000950170-98-000413.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003721/000095015201001730/0000950152-01-001730.txt</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1644,13 +1644,13 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -1661,18 +1661,18 @@
         <v>3721</v>
       </c>
       <c r="B29" t="n">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003721/000095015201001730/0000950152-01-001730.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003721/000095015200002296/0000950152-00-002296.txt</t>
         </is>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -1687,7 +1687,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -1704,18 +1704,18 @@
         <v>3721</v>
       </c>
       <c r="B30" t="n">
-        <v>1997</v>
+        <v>2001</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003721/000095015298002155/0000950152-98-002155.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003721/000095015202001411/0000950152-02-001411.txt</t>
         </is>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -1744,21 +1744,21 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>3753</v>
+        <v>3721</v>
       </c>
       <c r="B31" t="n">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003753/000000375302000003/0000003753-02-000003.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003721/000095015203003160/l99072be10vk.htm</t>
         </is>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1790,24 +1790,24 @@
         <v>3721</v>
       </c>
       <c r="B32" t="n">
-        <v>2001</v>
+        <v>1998</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003721/000095015202001411/0000950152-02-001411.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003721/000095015299002425/0000950152-99-002425.txt</t>
         </is>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1822,7 +1822,7 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -1833,18 +1833,18 @@
         <v>3753</v>
       </c>
       <c r="B33" t="n">
-        <v>2004</v>
+        <v>2001</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003753/000000375305000004/0000003753-05-000004.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003753/000000375302000003/0000003753-02-000003.txt</t>
         </is>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -1873,21 +1873,21 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>3721</v>
+        <v>3753</v>
       </c>
       <c r="B34" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003721/000095015203003160/l99072be10vk.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003753/000000375304000004/0000003753-04-000004.txt</t>
         </is>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -1919,11 +1919,11 @@
         <v>3952</v>
       </c>
       <c r="B35" t="n">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003952/000095016899000727/0000950168-99-000727.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003952/000095016998000361/0000950169-98-000361.txt</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1959,21 +1959,21 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>3952</v>
+        <v>3753</v>
       </c>
       <c r="B36" t="n">
-        <v>1997</v>
+        <v>2004</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003952/000095016998000361/0000950169-98-000361.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003753/000000375305000004/0000003753-05-000004.txt</t>
         </is>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -1994,7 +1994,7 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -2005,11 +2005,11 @@
         <v>3952</v>
       </c>
       <c r="B37" t="n">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003952/000095016900000255/0000950169-00-000255.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003952/000092838501000932/0000928385-01-000932.txt</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -2045,21 +2045,21 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>3753</v>
+        <v>3952</v>
       </c>
       <c r="B38" t="n">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003753/000000375304000004/0000003753-04-000004.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003952/000095016902000059/0000950169-02-000059.txt</t>
         </is>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -2074,13 +2074,13 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -2091,18 +2091,18 @@
         <v>3952</v>
       </c>
       <c r="B39" t="n">
-        <v>2000</v>
+        <v>2002</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003952/000092838501000932/0000928385-01-000932.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003952/000095016803000972/d10k.htm</t>
         </is>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -2117,7 +2117,7 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -2134,11 +2134,11 @@
         <v>3952</v>
       </c>
       <c r="B40" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003952/000095016803000972/d10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003952/000095013304000919/w94384e10vk.htm</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -2166,7 +2166,7 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -2177,11 +2177,11 @@
         <v>3952</v>
       </c>
       <c r="B41" t="n">
-        <v>2001</v>
+        <v>1999</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003952/000095016902000059/0000950169-02-000059.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003952/000095016900000255/0000950169-00-000255.txt</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -2203,7 +2203,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2220,18 +2220,18 @@
         <v>3952</v>
       </c>
       <c r="B42" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003952/000095013304000919/w94384e10vk.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003952/000095013305001407/w06130ae10vk.htm</t>
         </is>
       </c>
       <c r="D42" t="n">
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -2246,13 +2246,13 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -2263,21 +2263,21 @@
         <v>3952</v>
       </c>
       <c r="B43" t="n">
-        <v>2005</v>
+        <v>1998</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003952/000095013306004392/w25671e10vk.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003952/000095016899000727/0000950168-99-000727.txt</t>
         </is>
       </c>
       <c r="D43" t="n">
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -2306,21 +2306,21 @@
         <v>3952</v>
       </c>
       <c r="B44" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003952/000095013305001407/w06130ae10vk.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003952/000095013306004392/w25671e10vk.htm</t>
         </is>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -2332,7 +2332,7 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -2349,36 +2349,36 @@
         <v>3952</v>
       </c>
       <c r="B45" t="n">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003952/000095012310032721/c98488e10vk.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003952/000095013308001215/w51733e10vk.htm</t>
         </is>
       </c>
       <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>37</v>
+      </c>
+      <c r="F45" t="n">
+        <v>3</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
         <v>1</v>
       </c>
-      <c r="E45" t="n">
-        <v>28</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" t="n">
-        <v>3</v>
-      </c>
       <c r="K45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -2435,18 +2435,18 @@
         <v>3952</v>
       </c>
       <c r="B47" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003952/000095013308001215/w51733e10vk.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003952/000095013307001230/w31824e10vk.htm</t>
         </is>
       </c>
       <c r="D47" t="n">
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="F47" t="n">
         <v>3</v>
@@ -2461,13 +2461,13 @@
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -2475,21 +2475,21 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>3959</v>
+        <v>3982</v>
       </c>
       <c r="B48" t="n">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003959/000101540203001241/0001015402-03-001241.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003982/000089706901000272/0000897069-01-000272.txt</t>
         </is>
       </c>
       <c r="D48" t="n">
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -2561,21 +2561,21 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>3982</v>
+        <v>3952</v>
       </c>
       <c r="B50" t="n">
-        <v>2000</v>
+        <v>2009</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003982/000089706901000272/0000897069-01-000272.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003952/000095012310032721/c98488e10vk.htm</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -2590,10 +2590,10 @@
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -2604,24 +2604,24 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>3952</v>
+        <v>3959</v>
       </c>
       <c r="B51" t="n">
-        <v>2006</v>
+        <v>2002</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003952/000095013307001230/w31824e10vk.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003959/000101540203001241/0001015402-03-001241.txt</t>
         </is>
       </c>
       <c r="D51" t="n">
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="F51" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -2633,13 +2633,13 @@
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
@@ -2650,18 +2650,18 @@
         <v>3982</v>
       </c>
       <c r="B52" t="n">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003982/000101968704000803/0001019687-04-000803.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003982/000101968702000509/0001019687-02-000509.txt</t>
         </is>
       </c>
       <c r="D52" t="n">
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -2690,21 +2690,21 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>4127</v>
+        <v>3982</v>
       </c>
       <c r="B53" t="n">
-        <v>1996</v>
+        <v>2003</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004127/000092701696000491/0000927016-96-000491.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003982/000101968704000803/0001019687-04-000803.txt</t>
         </is>
       </c>
       <c r="D53" t="n">
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -2736,21 +2736,21 @@
         <v>3982</v>
       </c>
       <c r="B54" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003982/000095012906002926/h34263e10vk.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003982/000095012907001381/h44611e10vk.htm</t>
         </is>
       </c>
       <c r="D54" t="n">
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -2779,18 +2779,18 @@
         <v>3982</v>
       </c>
       <c r="B55" t="n">
-        <v>2002</v>
+        <v>2005</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003982/000101968703000751/0001019687-03-000751.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003982/000095012906002926/h34263e10vk.htm</t>
         </is>
       </c>
       <c r="D55" t="n">
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -2822,18 +2822,18 @@
         <v>3982</v>
       </c>
       <c r="B56" t="n">
-        <v>2010</v>
+        <v>2002</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003982/000119312511067128/d10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003982/000101968703000751/0001019687-03-000751.txt</t>
         </is>
       </c>
       <c r="D56" t="n">
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>94</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -2862,21 +2862,21 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>3982</v>
+        <v>4127</v>
       </c>
       <c r="B57" t="n">
-        <v>2008</v>
+        <v>1996</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003982/000095012909000822/h65969e10vk.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004127/000092701696000491/0000927016-96-000491.txt</t>
         </is>
       </c>
       <c r="D57" t="n">
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -2908,18 +2908,18 @@
         <v>3982</v>
       </c>
       <c r="B58" t="n">
-        <v>2001</v>
+        <v>2008</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003982/000101968702000509/0001019687-02-000509.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003982/000095012909000822/h65969e10vk.htm</t>
         </is>
       </c>
       <c r="D58" t="n">
         <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -2951,21 +2951,21 @@
         <v>3982</v>
       </c>
       <c r="B59" t="n">
-        <v>2006</v>
+        <v>2010</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003982/000095012907001381/h44611e10vk.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003982/000119312511067128/d10k.htm</t>
         </is>
       </c>
       <c r="D59" t="n">
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="F59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -3034,27 +3034,27 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>4127</v>
+        <v>4164</v>
       </c>
       <c r="B61" t="n">
-        <v>2022</v>
+        <v>1998</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004127/000000412722000038/swks-20220930.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004164/000104746998028558/0001047469-98-028558.txt</t>
         </is>
       </c>
       <c r="D61" t="n">
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -3120,14 +3120,14 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>4164</v>
+        <v>4127</v>
       </c>
       <c r="B63" t="n">
-        <v>1997</v>
+        <v>2022</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004164/000091205797025356/0000912057-97-025356.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004127/000000412722000038/swks-20220930.htm</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -3209,24 +3209,24 @@
         <v>4164</v>
       </c>
       <c r="B65" t="n">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004164/000104746998028558/0001047469-98-028558.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004164/000091205797025356/0000912057-97-025356.txt</t>
         </is>
       </c>
       <c r="D65" t="n">
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -3252,21 +3252,21 @@
         <v>4164</v>
       </c>
       <c r="B66" t="n">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004164/000114420406012752/v036165_10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004164/000114420404003756/0001144204-04-003756.txt</t>
         </is>
       </c>
       <c r="D66" t="n">
         <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -3281,7 +3281,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -3292,24 +3292,24 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>4187</v>
+        <v>4164</v>
       </c>
       <c r="B67" t="n">
-        <v>1999</v>
+        <v>2005</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000089230300000039/0000892303-00-000039.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004164/000114420406012752/v036165_10k.htm</t>
         </is>
       </c>
       <c r="D67" t="n">
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -3324,7 +3324,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
@@ -3338,11 +3338,11 @@
         <v>4187</v>
       </c>
       <c r="B68" t="n">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000089230301500007/isa10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000089230300000039/0000892303-00-000039.txt</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -3381,18 +3381,18 @@
         <v>4164</v>
       </c>
       <c r="B69" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004164/000114420404003756/0001144204-04-003756.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004164/000114420405009492/v015096.htm</t>
         </is>
       </c>
       <c r="D69" t="n">
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -3421,21 +3421,21 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>4164</v>
+        <v>4187</v>
       </c>
       <c r="B70" t="n">
-        <v>2004</v>
+        <v>1998</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004164/000114420405009492/v015096.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000089230399000022/0000892303-99-000022.txt</t>
         </is>
       </c>
       <c r="D70" t="n">
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -3467,18 +3467,18 @@
         <v>4187</v>
       </c>
       <c r="B71" t="n">
-        <v>1998</v>
+        <v>2005</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000089230399000022/0000892303-99-000022.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000089230306000026/isa10k12312005.htm</t>
         </is>
       </c>
       <c r="D71" t="n">
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
@@ -3510,11 +3510,11 @@
         <v>4187</v>
       </c>
       <c r="B72" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000089230306000026/isa10k12312005.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000089230307000035/isaform10k2007.htm</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -3553,11 +3553,11 @@
         <v>4187</v>
       </c>
       <c r="B73" t="n">
-        <v>2004</v>
+        <v>2007</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000089230305000077/isa10k12312004.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000089230308000021/isa10k12312007.htm</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -3596,11 +3596,11 @@
         <v>4187</v>
       </c>
       <c r="B74" t="n">
-        <v>2006</v>
+        <v>2000</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000089230307000035/isaform10k2007.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000089230301500007/isa10k.htm</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3639,11 +3639,11 @@
         <v>4187</v>
       </c>
       <c r="B75" t="n">
-        <v>2008</v>
+        <v>2004</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000089230309000030/isa10k12312008.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000089230305000077/isa10k12312004.htm</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3656,7 +3656,7 @@
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -3671,7 +3671,7 @@
         <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
@@ -3682,11 +3682,11 @@
         <v>4187</v>
       </c>
       <c r="B76" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000089230308000021/isa10k12312007.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000089230309000030/isa10k12312008.htm</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3699,7 +3699,7 @@
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -3714,7 +3714,7 @@
         <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
@@ -3811,24 +3811,24 @@
         <v>4187</v>
       </c>
       <c r="B79" t="n">
-        <v>2015</v>
+        <v>2010</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000000418716000034/idsa-20151231x10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000093041311002265/c64854_10k.htm</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F79" t="n">
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
@@ -3843,7 +3843,7 @@
         <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
@@ -3854,24 +3854,24 @@
         <v>4187</v>
       </c>
       <c r="B80" t="n">
-        <v>2010</v>
+        <v>2015</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000093041311002265/c64854_10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000000418716000034/idsa-20151231x10k.htm</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F80" t="n">
         <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -3886,7 +3886,7 @@
         <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
@@ -3897,24 +3897,24 @@
         <v>4187</v>
       </c>
       <c r="B81" t="n">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000089710117000405/idsa-20161231.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000000418714000020/idsa-20131231x10k1x11x14.htm</t>
         </is>
       </c>
       <c r="D81" t="n">
         <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -3929,7 +3929,7 @@
         <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M81" t="n">
         <v>0</v>
@@ -3940,24 +3940,24 @@
         <v>4187</v>
       </c>
       <c r="B82" t="n">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000089710119000205/MainDocument.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000089710117000405/idsa-20161231.htm</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -3983,24 +3983,24 @@
         <v>4187</v>
       </c>
       <c r="B83" t="n">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000000418713000010/a201210k1.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000162828015002303/idsa-20141231x10k.htm</t>
         </is>
       </c>
       <c r="D83" t="n">
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -4015,7 +4015,7 @@
         <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M83" t="n">
         <v>0</v>
@@ -4026,11 +4026,11 @@
         <v>4187</v>
       </c>
       <c r="B84" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000000418714000020/idsa-20131231x10k1x11x14.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000000418713000010/a201210k1.htm</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -4043,7 +4043,7 @@
         <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -4069,24 +4069,24 @@
         <v>4187</v>
       </c>
       <c r="B85" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000089710118000301/idsa-20171231.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000089710119000205/MainDocument.htm</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -4112,24 +4112,24 @@
         <v>4187</v>
       </c>
       <c r="B86" t="n">
-        <v>2014</v>
+        <v>2017</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000162828015002303/idsa-20141231x10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000089710118000301/idsa-20171231.htm</t>
         </is>
       </c>
       <c r="D86" t="n">
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -4144,7 +4144,7 @@
         <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
@@ -4198,11 +4198,11 @@
         <v>4281</v>
       </c>
       <c r="B88" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004281/000000428120000038/form10k4q19.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004281/000000428119000031/form10k_4q18.htm</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -4215,7 +4215,7 @@
         <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -4241,24 +4241,24 @@
         <v>4281</v>
       </c>
       <c r="B89" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004281/000000428121000049/arnc-20201231.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004281/000000428120000038/form10k4q19.htm</t>
         </is>
       </c>
       <c r="D89" t="n">
         <v>0</v>
       </c>
       <c r="E89" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" t="n">
         <v>2</v>
-      </c>
-      <c r="F89" t="n">
-        <v>0</v>
-      </c>
-      <c r="G89" t="n">
-        <v>1</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -4284,11 +4284,11 @@
         <v>4285</v>
       </c>
       <c r="B90" t="n">
-        <v>1999</v>
+        <v>1997</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004285/000095012300002901/0000950123-00-002901.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004285/000095012398003261/0000950123-98-003261.txt</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="L90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
         <v>0</v>
@@ -4327,18 +4327,18 @@
         <v>4281</v>
       </c>
       <c r="B91" t="n">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004281/000000428119000031/form10k_4q18.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004281/000000428122000004/hwm-20211231.htm</t>
         </is>
       </c>
       <c r="D91" t="n">
         <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -4359,7 +4359,7 @@
         <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
         <v>0</v>
@@ -4370,11 +4370,11 @@
         <v>4281</v>
       </c>
       <c r="B92" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004281/000000428122000004/hwm-20211231.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004281/000000428121000049/arnc-20201231.htm</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -4402,7 +4402,7 @@
         <v>0</v>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M92" t="n">
         <v>0</v>
@@ -4413,11 +4413,11 @@
         <v>4285</v>
       </c>
       <c r="B93" t="n">
-        <v>1997</v>
+        <v>2002</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004285/000095012398003261/0000950123-98-003261.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004285/000100329703000065/alcan10k.htm</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -4430,7 +4430,7 @@
         <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -4439,7 +4439,7 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -4499,11 +4499,11 @@
         <v>4285</v>
       </c>
       <c r="B95" t="n">
-        <v>2002</v>
+        <v>1999</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004285/000100329703000065/alcan10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004285/000095012300002901/0000950123-00-002901.txt</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -4516,7 +4516,7 @@
         <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -4525,13 +4525,13 @@
         <v>0</v>
       </c>
       <c r="J95" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" t="n">
         <v>1</v>
-      </c>
-      <c r="K95" t="n">
-        <v>0</v>
-      </c>
-      <c r="L95" t="n">
-        <v>0</v>
       </c>
       <c r="M95" t="n">
         <v>0</v>
@@ -4585,11 +4585,11 @@
         <v>4285</v>
       </c>
       <c r="B97" t="n">
-        <v>2004</v>
+        <v>2001</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004285/000100329705000061/alcanform10k1.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004285/000113031902000222/0001130319-02-000222.txt</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -4602,7 +4602,7 @@
         <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -4617,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M97" t="n">
         <v>0</v>
@@ -4671,11 +4671,11 @@
         <v>4285</v>
       </c>
       <c r="B99" t="n">
-        <v>2001</v>
+        <v>2005</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004285/000113031902000222/0001130319-02-000222.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004285/000000428506000006/form10k.htm</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -4688,7 +4688,7 @@
         <v>0</v>
       </c>
       <c r="G99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
         <v>0</v>
       </c>
       <c r="L99" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
         <v>0</v>
@@ -4714,11 +4714,11 @@
         <v>4285</v>
       </c>
       <c r="B100" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004285/000000428506000006/form10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004285/000100329705000061/alcanform10k1.htm</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -4757,18 +4757,18 @@
         <v>4310</v>
       </c>
       <c r="B101" t="n">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004310/000000431001000005/0000004310-01-000005.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004310/000000431000000007/0000004310-00-000007.txt</t>
         </is>
       </c>
       <c r="D101" t="n">
         <v>0</v>
       </c>
       <c r="E101" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F101" t="n">
         <v>0</v>
@@ -4840,21 +4840,21 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>4310</v>
+        <v>4317</v>
       </c>
       <c r="B103" t="n">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004310/000000431000000007/0000004310-00-000007.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004317/000091205796015710/0000912057-96-015710.txt</t>
         </is>
       </c>
       <c r="D103" t="n">
         <v>0</v>
       </c>
       <c r="E103" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F103" t="n">
         <v>0</v>
@@ -4883,21 +4883,21 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>4317</v>
+        <v>4310</v>
       </c>
       <c r="B104" t="n">
-        <v>1997</v>
+        <v>2000</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004317/000000431797000021/0000004317-97-000021.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004310/000000431001000005/0000004310-01-000005.txt</t>
         </is>
       </c>
       <c r="D104" t="n">
         <v>0</v>
       </c>
       <c r="E104" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F104" t="n">
         <v>0</v>
@@ -4972,18 +4972,18 @@
         <v>4317</v>
       </c>
       <c r="B106" t="n">
-        <v>1996</v>
+        <v>1999</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004317/000091205796015710/0000912057-96-015710.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004317/000104746999025714/0001047469-99-025714.txt</t>
         </is>
       </c>
       <c r="D106" t="n">
         <v>0</v>
       </c>
       <c r="E106" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="F106" t="n">
         <v>0</v>
@@ -5012,21 +5012,21 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>4310</v>
+        <v>4317</v>
       </c>
       <c r="B107" t="n">
         <v>1997</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004310/000000431098000004/0000004310-98-000004.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004317/000000431797000021/0000004317-97-000021.txt</t>
         </is>
       </c>
       <c r="D107" t="n">
         <v>0</v>
       </c>
       <c r="E107" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F107" t="n">
         <v>0</v>
@@ -5055,21 +5055,21 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>4317</v>
+        <v>4310</v>
       </c>
       <c r="B108" t="n">
-        <v>2001</v>
+        <v>1997</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004317/000091205701520587/a2052195z10ksb40.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004310/000000431098000004/0000004310-98-000004.txt</t>
         </is>
       </c>
       <c r="D108" t="n">
         <v>0</v>
       </c>
       <c r="E108" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F108" t="n">
         <v>0</v>
@@ -5101,18 +5101,18 @@
         <v>4317</v>
       </c>
       <c r="B109" t="n">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004317/000091205702025890/a2083304z10ksb.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004317/000091205700028904/0000912057-00-028904.txt</t>
         </is>
       </c>
       <c r="D109" t="n">
         <v>0</v>
       </c>
       <c r="E109" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="F109" t="n">
         <v>0</v>
@@ -5144,18 +5144,18 @@
         <v>4317</v>
       </c>
       <c r="B110" t="n">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004317/000104746999025714/0001047469-99-025714.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004317/000091205701520587/a2052195z10ksb40.htm</t>
         </is>
       </c>
       <c r="D110" t="n">
         <v>0</v>
       </c>
       <c r="E110" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F110" t="n">
         <v>0</v>
@@ -5273,18 +5273,18 @@
         <v>4317</v>
       </c>
       <c r="B113" t="n">
-        <v>2000</v>
+        <v>2005</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004317/000091205700028904/0000912057-00-028904.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004317/000104746905018253/a2160291z10ksb.htm</t>
         </is>
       </c>
       <c r="D113" t="n">
         <v>0</v>
       </c>
       <c r="E113" t="n">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="F113" t="n">
         <v>0</v>
@@ -5316,18 +5316,18 @@
         <v>4317</v>
       </c>
       <c r="B114" t="n">
-        <v>2005</v>
+        <v>2002</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004317/000104746905018253/a2160291z10ksb.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004317/000091205702025890/a2083304z10ksb.htm</t>
         </is>
       </c>
       <c r="D114" t="n">
         <v>0</v>
       </c>
       <c r="E114" t="n">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="F114" t="n">
         <v>0</v>
@@ -5359,18 +5359,18 @@
         <v>4447</v>
       </c>
       <c r="B115" t="n">
-        <v>2002</v>
+        <v>1997</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000095012303003289/y83989e10vk.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000095012398003112/0000950123-98-003112.txt</t>
         </is>
       </c>
       <c r="D115" t="n">
         <v>0</v>
       </c>
       <c r="E115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F115" t="n">
         <v>0</v>
@@ -5391,7 +5391,7 @@
         <v>0</v>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M115" t="n">
         <v>0</v>
@@ -5402,11 +5402,11 @@
         <v>4447</v>
       </c>
       <c r="B116" t="n">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000095012398003112/0000950123-98-003112.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000095012399002682/0000950123-99-002682.txt</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -5445,18 +5445,18 @@
         <v>4447</v>
       </c>
       <c r="B117" t="n">
-        <v>2001</v>
+        <v>1999</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000095012302003005/y57862e10-k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000095012300002763/0000950123-00-002763.txt</t>
         </is>
       </c>
       <c r="D117" t="n">
         <v>0</v>
       </c>
       <c r="E117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F117" t="n">
         <v>0</v>
@@ -5477,7 +5477,7 @@
         <v>0</v>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M117" t="n">
         <v>0</v>
@@ -5488,18 +5488,18 @@
         <v>4447</v>
       </c>
       <c r="B118" t="n">
-        <v>1998</v>
+        <v>2003</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000095012399002682/0000950123-99-002682.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000095012304003250/y93542e10vk.htm</t>
         </is>
       </c>
       <c r="D118" t="n">
         <v>0</v>
       </c>
       <c r="E118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F118" t="n">
         <v>0</v>
@@ -5520,7 +5520,7 @@
         <v>0</v>
       </c>
       <c r="L118" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
         <v>0</v>
@@ -5531,18 +5531,18 @@
         <v>4447</v>
       </c>
       <c r="B119" t="n">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000095012300002763/0000950123-00-002763.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000095012302003005/y57862e10-k.htm</t>
         </is>
       </c>
       <c r="D119" t="n">
         <v>0</v>
       </c>
       <c r="E119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F119" t="n">
         <v>0</v>
@@ -5563,7 +5563,7 @@
         <v>0</v>
       </c>
       <c r="L119" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
         <v>0</v>
@@ -5574,18 +5574,18 @@
         <v>4447</v>
       </c>
       <c r="B120" t="n">
-        <v>2000</v>
+        <v>2002</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000095012301002755/0000950123-01-002755.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000095012303003289/y83989e10vk.htm</t>
         </is>
       </c>
       <c r="D120" t="n">
         <v>0</v>
       </c>
       <c r="E120" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F120" t="n">
         <v>0</v>
@@ -5606,7 +5606,7 @@
         <v>0</v>
       </c>
       <c r="L120" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
         <v>0</v>
@@ -5617,18 +5617,18 @@
         <v>4447</v>
       </c>
       <c r="B121" t="n">
-        <v>2003</v>
+        <v>2000</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000095012304003250/y93542e10vk.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000095012301002755/0000950123-01-002755.txt</t>
         </is>
       </c>
       <c r="D121" t="n">
         <v>0</v>
       </c>
       <c r="E121" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F121" t="n">
         <v>0</v>
@@ -5649,7 +5649,7 @@
         <v>0</v>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M121" t="n">
         <v>0</v>
@@ -5660,11 +5660,11 @@
         <v>4447</v>
       </c>
       <c r="B122" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000095012306002849/y17683e10vk.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000095012305003078/y05893e10vk.htm</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -5703,11 +5703,11 @@
         <v>4447</v>
       </c>
       <c r="B123" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000095012305003078/y05893e10vk.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000095012306002849/y17683e10vk.htm</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -5746,15 +5746,15 @@
         <v>4447</v>
       </c>
       <c r="B124" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000095012309003700/y74825e10vk.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000095012308002199/y50075e10vk.htm</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E124" t="n">
         <v>1</v>
@@ -5832,15 +5832,15 @@
         <v>4447</v>
       </c>
       <c r="B126" t="n">
-        <v>2006</v>
+        <v>2008</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000095012307003008/y30212e10vk.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000095012309003700/y74825e10vk.htm</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E126" t="n">
         <v>1</v>
@@ -5875,11 +5875,11 @@
         <v>4447</v>
       </c>
       <c r="B127" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000095012308002199/y50075e10vk.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000095012307003008/y30212e10vk.htm</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -5918,19 +5918,19 @@
         <v>4447</v>
       </c>
       <c r="B128" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000095012311018415/y87868e10vk.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000119312512081827/d270298d10k.htm</t>
         </is>
       </c>
       <c r="D128" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" t="n">
         <v>2</v>
       </c>
-      <c r="E128" t="n">
-        <v>1</v>
-      </c>
       <c r="F128" t="n">
         <v>0</v>
       </c>
@@ -5947,7 +5947,7 @@
         <v>0</v>
       </c>
       <c r="K128" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L128" t="n">
         <v>4</v>
@@ -5961,15 +5961,15 @@
         <v>4447</v>
       </c>
       <c r="B129" t="n">
-        <v>2013</v>
+        <v>2010</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000119312514077565/d652042d10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000095012311018415/y87868e10vk.htm</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E129" t="n">
         <v>1</v>
@@ -5990,7 +5990,7 @@
         <v>0</v>
       </c>
       <c r="K129" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L129" t="n">
         <v>4</v>
@@ -6004,11 +6004,11 @@
         <v>4447</v>
       </c>
       <c r="B130" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000119312513084779/d457291d10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000119312514077565/d652042d10k.htm</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -6047,18 +6047,18 @@
         <v>4447</v>
       </c>
       <c r="B131" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000119312512081827/d270298d10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000119312513084779/d457291d10k.htm</t>
         </is>
       </c>
       <c r="D131" t="n">
         <v>0</v>
       </c>
       <c r="E131" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F131" t="n">
         <v>0</v>
@@ -6133,15 +6133,15 @@
         <v>4447</v>
       </c>
       <c r="B133" t="n">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000156459018002698/hes-10k_20171231.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000156459016013433/hes-10k_20151231.htm</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E133" t="n">
         <v>2</v>
@@ -6165,7 +6165,7 @@
         <v>10</v>
       </c>
       <c r="L133" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="M133" t="n">
         <v>0</v>
@@ -6176,11 +6176,11 @@
         <v>4447</v>
       </c>
       <c r="B134" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000156459016013433/hes-10k_20151231.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000156459017002225/hes-10k_20161231.htm</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -6208,7 +6208,7 @@
         <v>10</v>
       </c>
       <c r="L134" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M134" t="n">
         <v>0</v>
@@ -6219,15 +6219,15 @@
         <v>4447</v>
       </c>
       <c r="B135" t="n">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000162828021003531/hes-20201231.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000156459018002698/hes-10k_20171231.htm</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E135" t="n">
         <v>2</v>
@@ -6236,7 +6236,7 @@
         <v>0</v>
       </c>
       <c r="G135" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -6245,13 +6245,13 @@
         <v>0</v>
       </c>
       <c r="J135" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K135" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="L135" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="M135" t="n">
         <v>0</v>
@@ -6262,15 +6262,15 @@
         <v>4447</v>
       </c>
       <c r="B136" t="n">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000156459017002225/hes-10k_20161231.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000156459019003671/hes-10k_20181231.htm</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E136" t="n">
         <v>2</v>
@@ -6291,10 +6291,10 @@
         <v>0</v>
       </c>
       <c r="K136" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L136" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M136" t="n">
         <v>0</v>
@@ -6302,27 +6302,27 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>4457</v>
+        <v>4447</v>
       </c>
       <c r="B137" t="n">
-        <v>1996</v>
+        <v>2019</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445796000044/0000004457-96-000044.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000156459020005545/hes-10k_20191231.htm</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E137" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F137" t="n">
         <v>0</v>
       </c>
       <c r="G137" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -6331,13 +6331,13 @@
         <v>0</v>
       </c>
       <c r="J137" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K137" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L137" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M137" t="n">
         <v>0</v>
@@ -6348,15 +6348,15 @@
         <v>4447</v>
       </c>
       <c r="B138" t="n">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000156459019003671/hes-10k_20181231.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000162828021003531/hes-20201231.htm</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E138" t="n">
         <v>2</v>
@@ -6365,7 +6365,7 @@
         <v>0</v>
       </c>
       <c r="G138" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -6374,13 +6374,13 @@
         <v>0</v>
       </c>
       <c r="J138" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K138" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="L138" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M138" t="n">
         <v>0</v>
@@ -6388,27 +6388,27 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>4447</v>
+        <v>4457</v>
       </c>
       <c r="B139" t="n">
-        <v>2019</v>
+        <v>1996</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000156459020005545/hes-10k_20191231.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445796000044/0000004457-96-000044.txt</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E139" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F139" t="n">
         <v>0</v>
       </c>
       <c r="G139" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -6417,13 +6417,13 @@
         <v>0</v>
       </c>
       <c r="J139" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K139" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="L139" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M139" t="n">
         <v>0</v>
@@ -6431,27 +6431,27 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>4457</v>
+        <v>4447</v>
       </c>
       <c r="B140" t="n">
-        <v>1997</v>
+        <v>2021</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445797000016/0000004457-97-000016.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000162828022004524/hes-20211231.htm</t>
         </is>
       </c>
       <c r="D140" t="n">
         <v>0</v>
       </c>
       <c r="E140" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F140" t="n">
         <v>0</v>
       </c>
       <c r="G140" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
@@ -6460,13 +6460,13 @@
         <v>0</v>
       </c>
       <c r="J140" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K140" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L140" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M140" t="n">
         <v>0</v>
@@ -6477,18 +6477,18 @@
         <v>4457</v>
       </c>
       <c r="B141" t="n">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445798000023/0000004457-98-000023.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445797000016/0000004457-97-000016.txt</t>
         </is>
       </c>
       <c r="D141" t="n">
         <v>0</v>
       </c>
       <c r="E141" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F141" t="n">
         <v>0</v>
@@ -6517,27 +6517,27 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>4447</v>
+        <v>4457</v>
       </c>
       <c r="B142" t="n">
-        <v>2021</v>
+        <v>1998</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000162828022004524/hes-20211231.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445798000023/0000004457-98-000023.txt</t>
         </is>
       </c>
       <c r="D142" t="n">
         <v>0</v>
       </c>
       <c r="E142" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F142" t="n">
         <v>0</v>
       </c>
       <c r="G142" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -6546,13 +6546,13 @@
         <v>0</v>
       </c>
       <c r="J142" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K142" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="L142" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M142" t="n">
         <v>0</v>
@@ -6563,11 +6563,11 @@
         <v>4457</v>
       </c>
       <c r="B143" t="n">
-        <v>2001</v>
+        <v>1999</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445701500063/0000004457-01-500063.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445799000028/0000004457-99-000028.txt</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -6580,7 +6580,7 @@
         <v>0</v>
       </c>
       <c r="G143" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -6595,7 +6595,7 @@
         <v>0</v>
       </c>
       <c r="L143" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M143" t="n">
         <v>0</v>
@@ -6606,11 +6606,11 @@
         <v>4457</v>
       </c>
       <c r="B144" t="n">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445799000028/0000004457-99-000028.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445701500063/0000004457-01-500063.txt</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -6623,7 +6623,7 @@
         <v>0</v>
       </c>
       <c r="G144" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -6638,7 +6638,7 @@
         <v>0</v>
       </c>
       <c r="L144" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M144" t="n">
         <v>0</v>
@@ -6649,11 +6649,11 @@
         <v>4457</v>
       </c>
       <c r="B145" t="n">
-        <v>2000</v>
+        <v>2003</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445700000067/0000004457-00-000067.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000095015303001671/p67969e10vk.htm</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -6666,7 +6666,7 @@
         <v>0</v>
       </c>
       <c r="G145" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -6681,7 +6681,7 @@
         <v>0</v>
       </c>
       <c r="L145" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M145" t="n">
         <v>0</v>
@@ -6692,11 +6692,11 @@
         <v>4457</v>
       </c>
       <c r="B146" t="n">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000095015304001463/p69260e10vk.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000095015302001266/0000950153-02-001266.txt</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -6709,7 +6709,7 @@
         <v>0</v>
       </c>
       <c r="G146" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -6724,7 +6724,7 @@
         <v>0</v>
       </c>
       <c r="L146" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M146" t="n">
         <v>0</v>
@@ -6735,11 +6735,11 @@
         <v>4457</v>
       </c>
       <c r="B147" t="n">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445706000008/march200610-k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000095015304001463/p69260e10vk.htm</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -6767,7 +6767,7 @@
         <v>0</v>
       </c>
       <c r="L147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M147" t="n">
         <v>0</v>
@@ -6778,11 +6778,11 @@
         <v>4457</v>
       </c>
       <c r="B148" t="n">
-        <v>2008</v>
+        <v>2005</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445708000010/body10-k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000095015305001469/p70807e10vk.htm</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -6795,7 +6795,7 @@
         <v>0</v>
       </c>
       <c r="G148" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
@@ -6821,11 +6821,11 @@
         <v>4457</v>
       </c>
       <c r="B149" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000095015305001469/p70807e10vk.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445706000008/march200610-k.htm</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -6838,7 +6838,7 @@
         <v>0</v>
       </c>
       <c r="G149" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -6853,7 +6853,7 @@
         <v>0</v>
       </c>
       <c r="L149" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M149" t="n">
         <v>0</v>
@@ -6864,11 +6864,11 @@
         <v>4457</v>
       </c>
       <c r="B150" t="n">
-        <v>2003</v>
+        <v>2007</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000095015303001671/p67969e10vk.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445707000011/march200710-k.htm</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -6881,7 +6881,7 @@
         <v>0</v>
       </c>
       <c r="G150" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -6907,11 +6907,11 @@
         <v>4457</v>
       </c>
       <c r="B151" t="n">
-        <v>2007</v>
+        <v>2000</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445707000011/march200710-k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445700000067/0000004457-00-000067.txt</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -6924,7 +6924,7 @@
         <v>0</v>
       </c>
       <c r="G151" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -6939,7 +6939,7 @@
         <v>0</v>
       </c>
       <c r="L151" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M151" t="n">
         <v>0</v>
@@ -6993,11 +6993,11 @@
         <v>4457</v>
       </c>
       <c r="B153" t="n">
-        <v>2002</v>
+        <v>2008</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000095015302001266/0000950153-02-001266.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445708000010/body10-k.htm</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -7010,7 +7010,7 @@
         <v>0</v>
       </c>
       <c r="G153" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -7025,7 +7025,7 @@
         <v>0</v>
       </c>
       <c r="L153" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M153" t="n">
         <v>0</v>
@@ -7036,11 +7036,11 @@
         <v>4457</v>
       </c>
       <c r="B154" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445711000059/mar10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445710000021/body10-k.htm</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -7053,7 +7053,7 @@
         <v>0</v>
       </c>
       <c r="G154" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -7079,11 +7079,11 @@
         <v>4457</v>
       </c>
       <c r="B155" t="n">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445713000016/March201310KReport.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445711000059/mar10k.htm</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -7096,7 +7096,7 @@
         <v>0</v>
       </c>
       <c r="G155" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -7122,11 +7122,11 @@
         <v>4457</v>
       </c>
       <c r="B156" t="n">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445715000019/Mar201510K.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445713000016/March201310KReport.htm</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -7251,11 +7251,11 @@
         <v>4457</v>
       </c>
       <c r="B159" t="n">
-        <v>2010</v>
+        <v>2015</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445710000021/body10-k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445715000019/Mar201510K.htm</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -7268,7 +7268,7 @@
         <v>0</v>
       </c>
       <c r="G159" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -7294,11 +7294,11 @@
         <v>4457</v>
       </c>
       <c r="B160" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445719000024/march201910k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445718000016/March201810K.htm</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -7311,7 +7311,7 @@
         <v>0</v>
       </c>
       <c r="G160" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -7326,7 +7326,7 @@
         <v>1</v>
       </c>
       <c r="L160" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M160" t="n">
         <v>0</v>
@@ -7423,11 +7423,11 @@
         <v>4457</v>
       </c>
       <c r="B163" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445718000016/March201810K.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445719000024/march201910k.htm</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -7440,7 +7440,7 @@
         <v>0</v>
       </c>
       <c r="G163" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -7455,7 +7455,7 @@
         <v>1</v>
       </c>
       <c r="L163" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M163" t="n">
         <v>0</v>
@@ -7466,11 +7466,11 @@
         <v>4457</v>
       </c>
       <c r="B164" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445720000053/uhal-20200331.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445721000040/uhal-20210331.htm</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -7483,7 +7483,7 @@
         <v>0</v>
       </c>
       <c r="G164" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
@@ -7509,11 +7509,11 @@
         <v>4457</v>
       </c>
       <c r="B165" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445721000040/uhal-20210331.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445720000053/uhal-20200331.htm</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -7526,7 +7526,7 @@
         <v>0</v>
       </c>
       <c r="G165" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>

--- a/excel/keywords.xlsx
+++ b/excel/keywords.xlsx
@@ -543,18 +543,18 @@
         <v>3570</v>
       </c>
       <c r="B3" t="n">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000089924302000927/0000899243-02-000927.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000089924303000668/0000899243-03-000668.txt</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -572,7 +572,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -586,24 +586,24 @@
         <v>3570</v>
       </c>
       <c r="B4" t="n">
-        <v>2007</v>
+        <v>2001</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000119312508039317/d10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000089924302000927/0000899243-02-000927.txt</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -618,7 +618,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -629,24 +629,24 @@
         <v>3570</v>
       </c>
       <c r="B5" t="n">
-        <v>2002</v>
+        <v>2005</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000089924303000668/0000899243-03-000668.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000119312506051265/d10k.htm</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -672,24 +672,24 @@
         <v>3570</v>
       </c>
       <c r="B6" t="n">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000119312506051265/d10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000119312508039317/d10k.htm</t>
         </is>
       </c>
       <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
         <v>4</v>
       </c>
-      <c r="E6" t="n">
-        <v>49</v>
-      </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -758,24 +758,24 @@
         <v>3570</v>
       </c>
       <c r="B8" t="n">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000119312505046389/d10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000119312507041208/d10k.htm</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -787,10 +787,10 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -801,39 +801,39 @@
         <v>3570</v>
       </c>
       <c r="B9" t="n">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000119312507041208/d10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000119312505046389/d10k.htm</t>
         </is>
       </c>
       <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>66</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>1</v>
       </c>
-      <c r="E9" t="n">
-        <v>23</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -844,24 +844,24 @@
         <v>3570</v>
       </c>
       <c r="B10" t="n">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000000357011000026/cei201010k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000119312509040197/d10k.htm</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -873,10 +873,10 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -887,18 +887,18 @@
         <v>3570</v>
       </c>
       <c r="B11" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000119312509040197/d10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000000357010000005/form_10k.htm</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -913,10 +913,10 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
         <v>2</v>
@@ -930,11 +930,11 @@
         <v>3570</v>
       </c>
       <c r="B12" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000000357010000005/form_10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000000357011000026/cei201010k.htm</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -947,7 +947,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -956,13 +956,13 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -973,24 +973,24 @@
         <v>3570</v>
       </c>
       <c r="B13" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000000357013000036/cei2012form10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000000357014000031/cei2013form10k.htm</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1005,7 +1005,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1059,18 +1059,18 @@
         <v>3570</v>
       </c>
       <c r="B15" t="n">
-        <v>2013</v>
+        <v>2016</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000000357014000031/cei2013form10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000000357017000052/cei2016form10-k.htm</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -1091,7 +1091,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -1145,39 +1145,39 @@
         <v>3570</v>
       </c>
       <c r="B17" t="n">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000000357016000284/cei2015form10-k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000000357013000036/cei2012form10k.htm</t>
         </is>
       </c>
       <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>6</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>5</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -1188,11 +1188,11 @@
         <v>3570</v>
       </c>
       <c r="B18" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000000357019000030/cei2018form10-k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000000357018000031/cei2017form10-k.htm</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1231,24 +1231,24 @@
         <v>3570</v>
       </c>
       <c r="B19" t="n">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000000357020000043/cei2019form10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000000357016000284/cei2015form10-k.htm</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1257,13 +1257,13 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -1274,24 +1274,24 @@
         <v>3570</v>
       </c>
       <c r="B20" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000000357018000031/cei2017form10-k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000000357020000043/cei2019form10k.htm</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1300,13 +1300,13 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -1317,15 +1317,15 @@
         <v>3570</v>
       </c>
       <c r="B21" t="n">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000000357022000024/lng-20211231.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000000357019000030/cei2018form10-k.htm</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1343,13 +1343,13 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -1360,15 +1360,15 @@
         <v>3570</v>
       </c>
       <c r="B22" t="n">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000000357017000052/cei2016form10-k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000000357021000039/lng-20201231.htm</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -1377,7 +1377,7 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1386,13 +1386,13 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -1403,15 +1403,15 @@
         <v>3570</v>
       </c>
       <c r="B23" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000000357021000039/lng-20201231.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003570/000000357022000024/lng-20211231.htm</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -1429,13 +1429,13 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -1618,18 +1618,18 @@
         <v>3721</v>
       </c>
       <c r="B28" t="n">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003721/000095015201001730/0000950152-01-001730.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003721/000095015200002296/0000950152-00-002296.txt</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -1644,7 +1644,7 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1661,33 +1661,33 @@
         <v>3721</v>
       </c>
       <c r="B29" t="n">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003721/000095015200002296/0000950152-00-002296.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003721/000095015201001730/0000950152-01-001730.txt</t>
         </is>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
         <v>2</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -1701,21 +1701,21 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>3721</v>
+        <v>3753</v>
       </c>
       <c r="B30" t="n">
         <v>2001</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003721/000095015202001411/0000950152-02-001411.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003753/000000375302000003/0000003753-02-000003.txt</t>
         </is>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -1790,24 +1790,24 @@
         <v>3721</v>
       </c>
       <c r="B32" t="n">
-        <v>1998</v>
+        <v>2001</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003721/000095015299002425/0000950152-99-002425.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003721/000095015202001411/0000950152-02-001411.txt</t>
         </is>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1822,7 +1822,7 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -1833,18 +1833,18 @@
         <v>3753</v>
       </c>
       <c r="B33" t="n">
-        <v>2001</v>
+        <v>2003</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003753/000000375302000003/0000003753-02-000003.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003753/000000375304000004/0000003753-04-000004.txt</t>
         </is>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -1873,21 +1873,21 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>3753</v>
+        <v>3952</v>
       </c>
       <c r="B34" t="n">
-        <v>2003</v>
+        <v>1997</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003753/000000375304000004/0000003753-04-000004.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003952/000095016998000361/0000950169-98-000361.txt</t>
         </is>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -1908,7 +1908,7 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -1916,21 +1916,21 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>3952</v>
+        <v>3753</v>
       </c>
       <c r="B35" t="n">
-        <v>1997</v>
+        <v>2004</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003952/000095016998000361/0000950169-98-000361.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003753/000000375305000004/0000003753-05-000004.txt</t>
         </is>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -1951,7 +1951,7 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -1959,42 +1959,42 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>3753</v>
+        <v>3952</v>
       </c>
       <c r="B36" t="n">
-        <v>2004</v>
+        <v>1998</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003753/000000375305000004/0000003753-05-000004.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003952/000095016899000727/0000950168-99-000727.txt</t>
         </is>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
       <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
         <v>2</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -2005,11 +2005,11 @@
         <v>3952</v>
       </c>
       <c r="B37" t="n">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003952/000092838501000932/0000928385-01-000932.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003952/000095016900000255/0000950169-00-000255.txt</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -2048,18 +2048,18 @@
         <v>3952</v>
       </c>
       <c r="B38" t="n">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003952/000095016902000059/0000950169-02-000059.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003952/000095016803000972/d10k.htm</t>
         </is>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -2091,18 +2091,18 @@
         <v>3952</v>
       </c>
       <c r="B39" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003952/000095016803000972/d10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003952/000095016902000059/0000950169-02-000059.txt</t>
         </is>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -2134,18 +2134,18 @@
         <v>3952</v>
       </c>
       <c r="B40" t="n">
-        <v>2003</v>
+        <v>2000</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003952/000095013304000919/w94384e10vk.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003952/000092838501000932/0000928385-01-000932.txt</t>
         </is>
       </c>
       <c r="D40" t="n">
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -2160,13 +2160,13 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -2177,18 +2177,18 @@
         <v>3952</v>
       </c>
       <c r="B41" t="n">
-        <v>1999</v>
+        <v>2003</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003952/000095016900000255/0000950169-00-000255.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003952/000095013304000919/w94384e10vk.htm</t>
         </is>
       </c>
       <c r="D41" t="n">
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -2217,27 +2217,27 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>3952</v>
+        <v>3721</v>
       </c>
       <c r="B42" t="n">
-        <v>2004</v>
+        <v>1998</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003952/000095013305001407/w06130ae10vk.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003721/000095015299002425/0000950152-99-002425.txt</t>
         </is>
       </c>
       <c r="D42" t="n">
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -2252,7 +2252,7 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -2263,18 +2263,18 @@
         <v>3952</v>
       </c>
       <c r="B43" t="n">
-        <v>1998</v>
+        <v>2004</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003952/000095016899000727/0000950168-99-000727.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003952/000095013305001407/w06130ae10vk.htm</t>
         </is>
       </c>
       <c r="D43" t="n">
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -2349,18 +2349,18 @@
         <v>3952</v>
       </c>
       <c r="B45" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003952/000095013308001215/w51733e10vk.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003952/000095013307001230/w31824e10vk.htm</t>
         </is>
       </c>
       <c r="D45" t="n">
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="F45" t="n">
         <v>3</v>
@@ -2375,13 +2375,13 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -2389,21 +2389,21 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>3959</v>
+        <v>3952</v>
       </c>
       <c r="B46" t="n">
-        <v>2003</v>
+        <v>2009</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003959/000101540204002096/0001015402-04-002096.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003952/000095012310032721/c98488e10vk.htm</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -2418,10 +2418,10 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -2435,21 +2435,21 @@
         <v>3952</v>
       </c>
       <c r="B47" t="n">
-        <v>2006</v>
+        <v>2008</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003952/000095013307001230/w31824e10vk.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003952/000095013309000974/w73375e10vk.htm</t>
         </is>
       </c>
       <c r="D47" t="n">
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="F47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -2461,13 +2461,13 @@
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -2475,24 +2475,24 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>3982</v>
+        <v>3952</v>
       </c>
       <c r="B48" t="n">
-        <v>2000</v>
+        <v>2007</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003982/000089706901000272/0000897069-01-000272.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003952/000095013308001215/w51733e10vk.htm</t>
         </is>
       </c>
       <c r="D48" t="n">
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -2504,7 +2504,7 @@
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -2518,21 +2518,21 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>3952</v>
+        <v>3959</v>
       </c>
       <c r="B49" t="n">
-        <v>2008</v>
+        <v>2002</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003952/000095013309000974/w73375e10vk.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003959/000101540203001241/0001015402-03-001241.txt</t>
         </is>
       </c>
       <c r="D49" t="n">
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -2547,7 +2547,7 @@
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -2561,21 +2561,21 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>3952</v>
+        <v>3959</v>
       </c>
       <c r="B50" t="n">
-        <v>2009</v>
+        <v>2003</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003952/000095012310032721/c98488e10vk.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003959/000101540204002096/0001015402-04-002096.txt</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -2590,10 +2590,10 @@
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -2604,21 +2604,21 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>3959</v>
+        <v>3982</v>
       </c>
       <c r="B51" t="n">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003959/000101540203001241/0001015402-03-001241.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003982/000089706901000272/0000897069-01-000272.txt</t>
         </is>
       </c>
       <c r="D51" t="n">
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -2650,18 +2650,18 @@
         <v>3982</v>
       </c>
       <c r="B52" t="n">
-        <v>2001</v>
+        <v>2005</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003982/000101968702000509/0001019687-02-000509.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003982/000095012906002926/h34263e10vk.htm</t>
         </is>
       </c>
       <c r="D52" t="n">
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -2693,18 +2693,18 @@
         <v>3982</v>
       </c>
       <c r="B53" t="n">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003982/000101968704000803/0001019687-04-000803.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003982/000101968702000509/0001019687-02-000509.txt</t>
         </is>
       </c>
       <c r="D53" t="n">
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -2779,18 +2779,18 @@
         <v>3982</v>
       </c>
       <c r="B55" t="n">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003982/000095012906002926/h34263e10vk.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003982/000101968704000803/0001019687-04-000803.txt</t>
         </is>
       </c>
       <c r="D55" t="n">
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -2822,18 +2822,18 @@
         <v>3982</v>
       </c>
       <c r="B56" t="n">
-        <v>2002</v>
+        <v>2008</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003982/000101968703000751/0001019687-03-000751.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003982/000095012909000822/h65969e10vk.htm</t>
         </is>
       </c>
       <c r="D56" t="n">
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>94</v>
+        <v>14</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -2905,21 +2905,21 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>3982</v>
+        <v>4127</v>
       </c>
       <c r="B58" t="n">
-        <v>2008</v>
+        <v>2020</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003982/000095012909000822/h65969e10vk.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004127/000000412720000058/swks-20201002.htm</t>
         </is>
       </c>
       <c r="D58" t="n">
         <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -2948,21 +2948,21 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>3982</v>
+        <v>4127</v>
       </c>
       <c r="B59" t="n">
-        <v>2010</v>
+        <v>2021</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000003982/000119312511067128/d10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004127/000000412721000058/swks-20211001.htm</t>
         </is>
       </c>
       <c r="D59" t="n">
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -2991,21 +2991,21 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>4127</v>
+        <v>3982</v>
       </c>
       <c r="B60" t="n">
-        <v>2020</v>
+        <v>2002</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004127/000000412720000058/swks-20201002.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003982/000101968703000751/0001019687-03-000751.txt</t>
         </is>
       </c>
       <c r="D60" t="n">
         <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
@@ -3034,27 +3034,27 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>4164</v>
+        <v>3982</v>
       </c>
       <c r="B61" t="n">
-        <v>1998</v>
+        <v>2010</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004164/000104746998028558/0001047469-98-028558.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000003982/000119312511067128/d10k.htm</t>
         </is>
       </c>
       <c r="D61" t="n">
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -3080,11 +3080,11 @@
         <v>4127</v>
       </c>
       <c r="B62" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004127/000000412721000058/swks-20211001.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004127/000000412722000038/swks-20220930.htm</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -3120,27 +3120,27 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>4127</v>
+        <v>4164</v>
       </c>
       <c r="B63" t="n">
-        <v>2022</v>
+        <v>1998</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004127/000000412722000038/swks-20220930.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004164/000104746998028558/0001047469-98-028558.txt</t>
         </is>
       </c>
       <c r="D63" t="n">
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -3163,27 +3163,27 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>4164</v>
+        <v>4187</v>
       </c>
       <c r="B64" t="n">
-        <v>2002</v>
+        <v>1999</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004164/000104746903013411/a2106455z10-k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000089230300000039/0000892303-00-000039.txt</t>
         </is>
       </c>
       <c r="D64" t="n">
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -3209,24 +3209,24 @@
         <v>4164</v>
       </c>
       <c r="B65" t="n">
-        <v>1997</v>
+        <v>2002</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004164/000091205797025356/0000912057-97-025356.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004164/000104746903013411/a2106455z10-k.htm</t>
         </is>
       </c>
       <c r="D65" t="n">
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -3252,18 +3252,18 @@
         <v>4164</v>
       </c>
       <c r="B66" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004164/000114420404003756/0001144204-04-003756.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004164/000114420405009492/v015096.htm</t>
         </is>
       </c>
       <c r="D66" t="n">
         <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
@@ -3338,18 +3338,18 @@
         <v>4187</v>
       </c>
       <c r="B68" t="n">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000089230300000039/0000892303-00-000039.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000089230399000022/0000892303-99-000022.txt</t>
         </is>
       </c>
       <c r="D68" t="n">
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -3378,21 +3378,21 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>4164</v>
+        <v>4187</v>
       </c>
       <c r="B69" t="n">
-        <v>2004</v>
+        <v>2000</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004164/000114420405009492/v015096.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000089230301500007/isa10k.htm</t>
         </is>
       </c>
       <c r="D69" t="n">
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -3421,21 +3421,21 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>4187</v>
+        <v>4164</v>
       </c>
       <c r="B70" t="n">
-        <v>1998</v>
+        <v>2003</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000089230399000022/0000892303-99-000022.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004164/000114420404003756/0001144204-04-003756.txt</t>
         </is>
       </c>
       <c r="D70" t="n">
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -3464,14 +3464,14 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>4187</v>
+        <v>4164</v>
       </c>
       <c r="B71" t="n">
-        <v>2005</v>
+        <v>1997</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000089230306000026/isa10k12312005.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004164/000091205797025356/0000912057-97-025356.txt</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -3510,11 +3510,11 @@
         <v>4187</v>
       </c>
       <c r="B72" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000089230307000035/isaform10k2007.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000089230306000026/isa10k12312005.htm</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -3553,11 +3553,11 @@
         <v>4187</v>
       </c>
       <c r="B73" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000089230308000021/isa10k12312007.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000089230307000035/isaform10k2007.htm</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -3596,11 +3596,11 @@
         <v>4187</v>
       </c>
       <c r="B74" t="n">
-        <v>2000</v>
+        <v>2004</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000089230301500007/isa10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000089230305000077/isa10k12312004.htm</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3639,11 +3639,11 @@
         <v>4187</v>
       </c>
       <c r="B75" t="n">
-        <v>2004</v>
+        <v>2007</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000089230305000077/isa10k12312004.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000089230308000021/isa10k12312007.htm</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3682,11 +3682,11 @@
         <v>4187</v>
       </c>
       <c r="B76" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000089230309000030/isa10k12312008.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000093041310001532/c60754_10k.htm</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3699,7 +3699,7 @@
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -3714,7 +3714,7 @@
         <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
@@ -3725,11 +3725,11 @@
         <v>4187</v>
       </c>
       <c r="B77" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000093041310001532/c60754_10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000093041311002265/c64854_10k.htm</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3742,7 +3742,7 @@
         <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -3757,7 +3757,7 @@
         <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M77" t="n">
         <v>0</v>
@@ -3768,11 +3768,11 @@
         <v>4187</v>
       </c>
       <c r="B78" t="n">
-        <v>2011</v>
+        <v>2008</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000093041312001385/c68719_10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000089230309000030/isa10k12312008.htm</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3785,7 +3785,7 @@
         <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -3800,7 +3800,7 @@
         <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M78" t="n">
         <v>0</v>
@@ -3811,11 +3811,11 @@
         <v>4187</v>
       </c>
       <c r="B79" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000093041311002265/c64854_10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000093041312001385/c68719_10k.htm</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3828,7 +3828,7 @@
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
@@ -3854,39 +3854,39 @@
         <v>4187</v>
       </c>
       <c r="B80" t="n">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000000418716000034/idsa-20151231x10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000000418714000020/idsa-20131231x10k1x11x14.htm</t>
         </is>
       </c>
       <c r="D80" t="n">
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F80" t="n">
         <v>0</v>
       </c>
       <c r="G80" t="n">
+        <v>15</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
         <v>7</v>
-      </c>
-      <c r="H80" t="n">
-        <v>0</v>
-      </c>
-      <c r="I80" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" t="n">
-        <v>0</v>
-      </c>
-      <c r="K80" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" t="n">
-        <v>2</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
@@ -3897,24 +3897,24 @@
         <v>4187</v>
       </c>
       <c r="B81" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000000418714000020/idsa-20131231x10k1x11x14.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000162828015002303/idsa-20141231x10k.htm</t>
         </is>
       </c>
       <c r="D81" t="n">
         <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -3929,7 +3929,7 @@
         <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M81" t="n">
         <v>0</v>
@@ -3940,24 +3940,24 @@
         <v>4187</v>
       </c>
       <c r="B82" t="n">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000089710117000405/idsa-20161231.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000000418713000010/a201210k1.htm</t>
         </is>
       </c>
       <c r="D82" t="n">
         <v>1</v>
       </c>
       <c r="E82" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -3972,7 +3972,7 @@
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M82" t="n">
         <v>0</v>
@@ -3983,24 +3983,24 @@
         <v>4187</v>
       </c>
       <c r="B83" t="n">
-        <v>2014</v>
+        <v>2018</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000162828015002303/idsa-20141231x10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000089710119000205/MainDocument.htm</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -4015,7 +4015,7 @@
         <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
         <v>0</v>
@@ -4026,24 +4026,24 @@
         <v>4187</v>
       </c>
       <c r="B84" t="n">
-        <v>2012</v>
+        <v>2015</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000000418713000010/a201210k1.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000000418716000034/idsa-20151231x10k.htm</t>
         </is>
       </c>
       <c r="D84" t="n">
         <v>1</v>
       </c>
       <c r="E84" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F84" t="n">
         <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -4058,7 +4058,7 @@
         <v>0</v>
       </c>
       <c r="L84" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M84" t="n">
         <v>0</v>
@@ -4069,24 +4069,24 @@
         <v>4187</v>
       </c>
       <c r="B85" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000089710119000205/MainDocument.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000089710118000301/idsa-20171231.htm</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E85" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -4112,11 +4112,11 @@
         <v>4187</v>
       </c>
       <c r="B86" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000089710118000301/idsa-20171231.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004187/000089710117000405/idsa-20161231.htm</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -4129,7 +4129,7 @@
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -4155,11 +4155,11 @@
         <v>4281</v>
       </c>
       <c r="B87" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004281/000000428118000042/form10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004281/000000428119000031/form10k_4q18.htm</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -4184,7 +4184,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L87" t="n">
         <v>2</v>
@@ -4198,11 +4198,11 @@
         <v>4281</v>
       </c>
       <c r="B88" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004281/000000428119000031/form10k_4q18.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004281/000000428118000042/form10k.htm</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -4227,7 +4227,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L88" t="n">
         <v>2</v>
@@ -4238,14 +4238,14 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>4281</v>
+        <v>4285</v>
       </c>
       <c r="B89" t="n">
-        <v>2019</v>
+        <v>1997</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004281/000000428120000038/form10k4q19.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004285/000095012398003261/0000950123-98-003261.txt</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -4273,7 +4273,7 @@
         <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
         <v>0</v>
@@ -4281,42 +4281,42 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>4285</v>
+        <v>4281</v>
       </c>
       <c r="B90" t="n">
-        <v>1997</v>
+        <v>2020</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004285/000095012398003261/0000950123-98-003261.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004281/000000428121000049/arnc-20201231.htm</t>
         </is>
       </c>
       <c r="D90" t="n">
         <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
       </c>
       <c r="G90" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="n">
         <v>2</v>
-      </c>
-      <c r="H90" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" t="n">
-        <v>0</v>
       </c>
       <c r="M90" t="n">
         <v>0</v>
@@ -4324,27 +4324,27 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>4281</v>
+        <v>4285</v>
       </c>
       <c r="B91" t="n">
-        <v>2021</v>
+        <v>1998</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004281/000000428122000004/hwm-20211231.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004285/000095012399002749/0000950123-99-002749.txt</t>
         </is>
       </c>
       <c r="D91" t="n">
         <v>0</v>
       </c>
       <c r="E91" t="n">
+        <v>10</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" t="n">
         <v>2</v>
-      </c>
-      <c r="F91" t="n">
-        <v>0</v>
-      </c>
-      <c r="G91" t="n">
-        <v>1</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -4367,42 +4367,42 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>4281</v>
+        <v>4285</v>
       </c>
       <c r="B92" t="n">
-        <v>2020</v>
+        <v>1999</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004281/000000428121000049/arnc-20201231.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004285/000095012300002901/0000950123-00-002901.txt</t>
         </is>
       </c>
       <c r="D92" t="n">
         <v>0</v>
       </c>
       <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" t="n">
         <v>2</v>
       </c>
-      <c r="F92" t="n">
-        <v>0</v>
-      </c>
-      <c r="G92" t="n">
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" t="n">
         <v>1</v>
-      </c>
-      <c r="H92" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92" t="n">
-        <v>0</v>
-      </c>
-      <c r="J92" t="n">
-        <v>0</v>
-      </c>
-      <c r="K92" t="n">
-        <v>0</v>
-      </c>
-      <c r="L92" t="n">
-        <v>2</v>
       </c>
       <c r="M92" t="n">
         <v>0</v>
@@ -4410,14 +4410,14 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>4285</v>
+        <v>4281</v>
       </c>
       <c r="B93" t="n">
-        <v>2002</v>
+        <v>2019</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004285/000100329703000065/alcan10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004281/000000428120000038/form10k4q19.htm</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -4430,7 +4430,7 @@
         <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -4439,13 +4439,13 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M93" t="n">
         <v>0</v>
@@ -4456,18 +4456,18 @@
         <v>4285</v>
       </c>
       <c r="B94" t="n">
-        <v>1998</v>
+        <v>2000</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004285/000095012399002749/0000950123-99-002749.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004285/000095012301002940/0000950123-01-002940.txt</t>
         </is>
       </c>
       <c r="D94" t="n">
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
@@ -4482,13 +4482,13 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M94" t="n">
         <v>0</v>
@@ -4499,11 +4499,11 @@
         <v>4285</v>
       </c>
       <c r="B95" t="n">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004285/000095012300002901/0000950123-00-002901.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004285/000113031902000222/0001130319-02-000222.txt</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -4525,13 +4525,13 @@
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M95" t="n">
         <v>0</v>
@@ -4542,24 +4542,24 @@
         <v>4285</v>
       </c>
       <c r="B96" t="n">
-        <v>2000</v>
+        <v>2002</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004285/000095012301002940/0000950123-01-002940.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004285/000100329703000065/alcan10k.htm</t>
         </is>
       </c>
       <c r="D96" t="n">
         <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
         <v>0</v>
       </c>
       <c r="L96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
         <v>0</v>
@@ -4582,27 +4582,27 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>4285</v>
+        <v>4281</v>
       </c>
       <c r="B97" t="n">
-        <v>2001</v>
+        <v>2021</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004285/000113031902000222/0001130319-02-000222.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004281/000000428122000004/hwm-20211231.htm</t>
         </is>
       </c>
       <c r="D97" t="n">
         <v>0</v>
       </c>
       <c r="E97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F97" t="n">
         <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -4611,13 +4611,13 @@
         <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K97" t="n">
         <v>0</v>
       </c>
       <c r="L97" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
         <v>0</v>
@@ -4628,18 +4628,18 @@
         <v>4285</v>
       </c>
       <c r="B98" t="n">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004285/000000428504000004/form10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004285/000000428506000006/form10k.htm</t>
         </is>
       </c>
       <c r="D98" t="n">
         <v>0</v>
       </c>
       <c r="E98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F98" t="n">
         <v>0</v>
@@ -4671,18 +4671,18 @@
         <v>4285</v>
       </c>
       <c r="B99" t="n">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004285/000000428506000006/form10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004285/000000428504000004/form10k.htm</t>
         </is>
       </c>
       <c r="D99" t="n">
         <v>0</v>
       </c>
       <c r="E99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F99" t="n">
         <v>0</v>
@@ -4711,21 +4711,21 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>4285</v>
+        <v>4310</v>
       </c>
       <c r="B100" t="n">
-        <v>2004</v>
+        <v>1998</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004285/000100329705000061/alcanform10k1.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004310/000000431099000010/0000004310-99-000010.txt</t>
         </is>
       </c>
       <c r="D100" t="n">
         <v>0</v>
       </c>
       <c r="E100" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F100" t="n">
         <v>0</v>
@@ -4740,7 +4740,7 @@
         <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K100" t="n">
         <v>0</v>
@@ -4754,21 +4754,21 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>4310</v>
+        <v>4285</v>
       </c>
       <c r="B101" t="n">
-        <v>1999</v>
+        <v>2004</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004310/000000431000000007/0000004310-00-000007.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004285/000100329705000061/alcanform10k1.htm</t>
         </is>
       </c>
       <c r="D101" t="n">
         <v>0</v>
       </c>
       <c r="E101" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F101" t="n">
         <v>0</v>
@@ -4783,7 +4783,7 @@
         <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K101" t="n">
         <v>0</v>
@@ -4797,21 +4797,21 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>4310</v>
+        <v>4317</v>
       </c>
       <c r="B102" t="n">
-        <v>1998</v>
+        <v>1996</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004310/000000431099000010/0000004310-99-000010.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004317/000091205796015710/0000912057-96-015710.txt</t>
         </is>
       </c>
       <c r="D102" t="n">
         <v>0</v>
       </c>
       <c r="E102" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F102" t="n">
         <v>0</v>
@@ -4840,21 +4840,21 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>4317</v>
+        <v>4310</v>
       </c>
       <c r="B103" t="n">
-        <v>1996</v>
+        <v>1999</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004317/000091205796015710/0000912057-96-015710.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004310/000000431000000007/0000004310-00-000007.txt</t>
         </is>
       </c>
       <c r="D103" t="n">
         <v>0</v>
       </c>
       <c r="E103" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F103" t="n">
         <v>0</v>
@@ -4886,18 +4886,18 @@
         <v>4310</v>
       </c>
       <c r="B104" t="n">
-        <v>2000</v>
+        <v>1997</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004310/000000431001000005/0000004310-01-000005.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004310/000000431098000004/0000004310-98-000004.txt</t>
         </is>
       </c>
       <c r="D104" t="n">
         <v>0</v>
       </c>
       <c r="E104" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F104" t="n">
         <v>0</v>
@@ -4969,21 +4969,21 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>4317</v>
+        <v>4310</v>
       </c>
       <c r="B106" t="n">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004317/000104746999025714/0001047469-99-025714.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004310/000000431001000005/0000004310-01-000005.txt</t>
         </is>
       </c>
       <c r="D106" t="n">
         <v>0</v>
       </c>
       <c r="E106" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="F106" t="n">
         <v>0</v>
@@ -5055,21 +5055,21 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>4310</v>
+        <v>4317</v>
       </c>
       <c r="B108" t="n">
-        <v>1997</v>
+        <v>2001</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004310/000000431098000004/0000004310-98-000004.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004317/000091205701520587/a2052195z10ksb40.htm</t>
         </is>
       </c>
       <c r="D108" t="n">
         <v>0</v>
       </c>
       <c r="E108" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F108" t="n">
         <v>0</v>
@@ -5144,18 +5144,18 @@
         <v>4317</v>
       </c>
       <c r="B110" t="n">
-        <v>2001</v>
+        <v>2004</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004317/000091205701520587/a2052195z10ksb40.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004317/000104746904018030/a2136982z10ksb.htm</t>
         </is>
       </c>
       <c r="D110" t="n">
         <v>0</v>
       </c>
       <c r="E110" t="n">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="F110" t="n">
         <v>0</v>
@@ -5187,18 +5187,18 @@
         <v>4317</v>
       </c>
       <c r="B111" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004317/000104746903022817/a2113625z10ksb.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004317/000091205702025890/a2083304z10ksb.htm</t>
         </is>
       </c>
       <c r="D111" t="n">
         <v>0</v>
       </c>
       <c r="E111" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F111" t="n">
         <v>0</v>
@@ -5230,18 +5230,18 @@
         <v>4317</v>
       </c>
       <c r="B112" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004317/000104746904018030/a2136982z10ksb.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004317/000104746905018253/a2160291z10ksb.htm</t>
         </is>
       </c>
       <c r="D112" t="n">
         <v>0</v>
       </c>
       <c r="E112" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F112" t="n">
         <v>0</v>
@@ -5273,18 +5273,18 @@
         <v>4317</v>
       </c>
       <c r="B113" t="n">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004317/000104746905018253/a2160291z10ksb.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004317/000104746903022817/a2113625z10ksb.htm</t>
         </is>
       </c>
       <c r="D113" t="n">
         <v>0</v>
       </c>
       <c r="E113" t="n">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="F113" t="n">
         <v>0</v>
@@ -5313,21 +5313,21 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>4317</v>
+        <v>4447</v>
       </c>
       <c r="B114" t="n">
-        <v>2002</v>
+        <v>1997</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004317/000091205702025890/a2083304z10ksb.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000095012398003112/0000950123-98-003112.txt</t>
         </is>
       </c>
       <c r="D114" t="n">
         <v>0</v>
       </c>
       <c r="E114" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="F114" t="n">
         <v>0</v>
@@ -5348,7 +5348,7 @@
         <v>0</v>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M114" t="n">
         <v>0</v>
@@ -5356,21 +5356,21 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>4447</v>
+        <v>4317</v>
       </c>
       <c r="B115" t="n">
-        <v>1997</v>
+        <v>1999</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000095012398003112/0000950123-98-003112.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004317/000104746999025714/0001047469-99-025714.txt</t>
         </is>
       </c>
       <c r="D115" t="n">
         <v>0</v>
       </c>
       <c r="E115" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="F115" t="n">
         <v>0</v>
@@ -5391,7 +5391,7 @@
         <v>0</v>
       </c>
       <c r="L115" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
         <v>0</v>
@@ -5402,11 +5402,11 @@
         <v>4447</v>
       </c>
       <c r="B116" t="n">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000095012399002682/0000950123-99-002682.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000095012300002763/0000950123-00-002763.txt</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -5434,7 +5434,7 @@
         <v>0</v>
       </c>
       <c r="L116" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M116" t="n">
         <v>0</v>
@@ -5445,18 +5445,18 @@
         <v>4447</v>
       </c>
       <c r="B117" t="n">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000095012300002763/0000950123-00-002763.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000095012302003005/y57862e10-k.htm</t>
         </is>
       </c>
       <c r="D117" t="n">
         <v>0</v>
       </c>
       <c r="E117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F117" t="n">
         <v>0</v>
@@ -5477,7 +5477,7 @@
         <v>0</v>
       </c>
       <c r="L117" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
         <v>0</v>
@@ -5488,18 +5488,18 @@
         <v>4447</v>
       </c>
       <c r="B118" t="n">
-        <v>2003</v>
+        <v>1998</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000095012304003250/y93542e10vk.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000095012399002682/0000950123-99-002682.txt</t>
         </is>
       </c>
       <c r="D118" t="n">
         <v>0</v>
       </c>
       <c r="E118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F118" t="n">
         <v>0</v>
@@ -5520,7 +5520,7 @@
         <v>0</v>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M118" t="n">
         <v>0</v>
@@ -5531,11 +5531,11 @@
         <v>4447</v>
       </c>
       <c r="B119" t="n">
-        <v>2001</v>
+        <v>2003</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000095012302003005/y57862e10-k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000095012304003250/y93542e10vk.htm</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -5703,11 +5703,11 @@
         <v>4447</v>
       </c>
       <c r="B123" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000095012306002849/y17683e10vk.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000095012307003008/y30212e10vk.htm</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -5746,11 +5746,11 @@
         <v>4447</v>
       </c>
       <c r="B124" t="n">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000095012308002199/y50075e10vk.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000095012306002849/y17683e10vk.htm</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -5789,15 +5789,15 @@
         <v>4447</v>
       </c>
       <c r="B125" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000095012310018336/y80747e10vk.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000095012309003700/y74825e10vk.htm</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E125" t="n">
         <v>1</v>
@@ -5818,10 +5818,10 @@
         <v>0</v>
       </c>
       <c r="K125" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L125" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M125" t="n">
         <v>0</v>
@@ -5832,15 +5832,15 @@
         <v>4447</v>
       </c>
       <c r="B126" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000095012309003700/y74825e10vk.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000095012308002199/y50075e10vk.htm</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E126" t="n">
         <v>1</v>
@@ -5875,15 +5875,15 @@
         <v>4447</v>
       </c>
       <c r="B127" t="n">
-        <v>2006</v>
+        <v>2009</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000095012307003008/y30212e10vk.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000095012310018336/y80747e10vk.htm</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E127" t="n">
         <v>1</v>
@@ -5904,10 +5904,10 @@
         <v>0</v>
       </c>
       <c r="K127" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L127" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M127" t="n">
         <v>0</v>
@@ -5918,18 +5918,18 @@
         <v>4447</v>
       </c>
       <c r="B128" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000119312512081827/d270298d10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000095012311018415/y87868e10vk.htm</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F128" t="n">
         <v>0</v>
@@ -5947,7 +5947,7 @@
         <v>0</v>
       </c>
       <c r="K128" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L128" t="n">
         <v>4</v>
@@ -5961,19 +5961,19 @@
         <v>4447</v>
       </c>
       <c r="B129" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000095012311018415/y87868e10vk.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000119312512081827/d270298d10k.htm</t>
         </is>
       </c>
       <c r="D129" t="n">
+        <v>0</v>
+      </c>
+      <c r="E129" t="n">
         <v>2</v>
       </c>
-      <c r="E129" t="n">
-        <v>1</v>
-      </c>
       <c r="F129" t="n">
         <v>0</v>
       </c>
@@ -5990,7 +5990,7 @@
         <v>0</v>
       </c>
       <c r="K129" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L129" t="n">
         <v>4</v>
@@ -6004,11 +6004,11 @@
         <v>4447</v>
       </c>
       <c r="B130" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000119312514077565/d652042d10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000119312513084779/d457291d10k.htm</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -6047,11 +6047,11 @@
         <v>4447</v>
       </c>
       <c r="B131" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000119312513084779/d457291d10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000119312514077565/d652042d10k.htm</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -6090,18 +6090,18 @@
         <v>4447</v>
       </c>
       <c r="B132" t="n">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000156459015001040/hes-10k_20141231.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000156459017002225/hes-10k_20161231.htm</t>
         </is>
       </c>
       <c r="D132" t="n">
         <v>0</v>
       </c>
       <c r="E132" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F132" t="n">
         <v>0</v>
@@ -6119,10 +6119,10 @@
         <v>0</v>
       </c>
       <c r="K132" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L132" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M132" t="n">
         <v>0</v>
@@ -6133,18 +6133,18 @@
         <v>4447</v>
       </c>
       <c r="B133" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000156459016013433/hes-10k_20151231.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000156459015001040/hes-10k_20141231.htm</t>
         </is>
       </c>
       <c r="D133" t="n">
         <v>0</v>
       </c>
       <c r="E133" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F133" t="n">
         <v>0</v>
@@ -6162,10 +6162,10 @@
         <v>0</v>
       </c>
       <c r="K133" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L133" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M133" t="n">
         <v>0</v>
@@ -6176,11 +6176,11 @@
         <v>4447</v>
       </c>
       <c r="B134" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000156459017002225/hes-10k_20161231.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000156459016013433/hes-10k_20151231.htm</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -6208,7 +6208,7 @@
         <v>10</v>
       </c>
       <c r="L134" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M134" t="n">
         <v>0</v>
@@ -6262,11 +6262,11 @@
         <v>4447</v>
       </c>
       <c r="B136" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000156459019003671/hes-10k_20181231.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000156459020005545/hes-10k_20191231.htm</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -6279,7 +6279,7 @@
         <v>0</v>
       </c>
       <c r="G136" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -6288,13 +6288,13 @@
         <v>0</v>
       </c>
       <c r="J136" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K136" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="L136" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M136" t="n">
         <v>0</v>
@@ -6305,11 +6305,11 @@
         <v>4447</v>
       </c>
       <c r="B137" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000156459020005545/hes-10k_20191231.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000156459019003671/hes-10k_20181231.htm</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -6322,7 +6322,7 @@
         <v>0</v>
       </c>
       <c r="G137" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -6331,13 +6331,13 @@
         <v>0</v>
       </c>
       <c r="J137" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K137" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="L137" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M137" t="n">
         <v>0</v>
@@ -6431,27 +6431,27 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>4447</v>
+        <v>4457</v>
       </c>
       <c r="B140" t="n">
-        <v>2021</v>
+        <v>1998</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000162828022004524/hes-20211231.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445798000023/0000004457-98-000023.txt</t>
         </is>
       </c>
       <c r="D140" t="n">
         <v>0</v>
       </c>
       <c r="E140" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F140" t="n">
         <v>0</v>
       </c>
       <c r="G140" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
@@ -6460,13 +6460,13 @@
         <v>0</v>
       </c>
       <c r="J140" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K140" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="L140" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M140" t="n">
         <v>0</v>
@@ -6520,11 +6520,11 @@
         <v>4457</v>
       </c>
       <c r="B142" t="n">
-        <v>1998</v>
+        <v>2000</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445798000023/0000004457-98-000023.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445700000067/0000004457-00-000067.txt</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -6537,7 +6537,7 @@
         <v>0</v>
       </c>
       <c r="G142" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -6552,7 +6552,7 @@
         <v>0</v>
       </c>
       <c r="L142" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M142" t="n">
         <v>0</v>
@@ -6563,11 +6563,11 @@
         <v>4457</v>
       </c>
       <c r="B143" t="n">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445799000028/0000004457-99-000028.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445701500063/0000004457-01-500063.txt</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -6580,7 +6580,7 @@
         <v>0</v>
       </c>
       <c r="G143" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -6595,7 +6595,7 @@
         <v>0</v>
       </c>
       <c r="L143" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M143" t="n">
         <v>0</v>
@@ -6603,27 +6603,27 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>4457</v>
+        <v>4447</v>
       </c>
       <c r="B144" t="n">
-        <v>2001</v>
+        <v>2021</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445701500063/0000004457-01-500063.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004447/000162828022004524/hes-20211231.htm</t>
         </is>
       </c>
       <c r="D144" t="n">
         <v>0</v>
       </c>
       <c r="E144" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F144" t="n">
         <v>0</v>
       </c>
       <c r="G144" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -6632,10 +6632,10 @@
         <v>0</v>
       </c>
       <c r="J144" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K144" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L144" t="n">
         <v>5</v>
@@ -6649,11 +6649,11 @@
         <v>4457</v>
       </c>
       <c r="B145" t="n">
-        <v>2003</v>
+        <v>1999</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000095015303001671/p67969e10vk.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445799000028/0000004457-99-000028.txt</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -6666,7 +6666,7 @@
         <v>0</v>
       </c>
       <c r="G145" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -6681,7 +6681,7 @@
         <v>0</v>
       </c>
       <c r="L145" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M145" t="n">
         <v>0</v>
@@ -6735,11 +6735,11 @@
         <v>4457</v>
       </c>
       <c r="B147" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000095015304001463/p69260e10vk.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000095015305001469/p70807e10vk.htm</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -6752,7 +6752,7 @@
         <v>0</v>
       </c>
       <c r="G147" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -6767,7 +6767,7 @@
         <v>0</v>
       </c>
       <c r="L147" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M147" t="n">
         <v>0</v>
@@ -6778,11 +6778,11 @@
         <v>4457</v>
       </c>
       <c r="B148" t="n">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000095015305001469/p70807e10vk.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000095015303001671/p67969e10vk.htm</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -6795,7 +6795,7 @@
         <v>0</v>
       </c>
       <c r="G148" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
@@ -6810,7 +6810,7 @@
         <v>0</v>
       </c>
       <c r="L148" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M148" t="n">
         <v>0</v>
@@ -6821,11 +6821,11 @@
         <v>4457</v>
       </c>
       <c r="B149" t="n">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445706000008/march200610-k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000095015304001463/p69260e10vk.htm</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -6853,7 +6853,7 @@
         <v>0</v>
       </c>
       <c r="L149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M149" t="n">
         <v>0</v>
@@ -6864,11 +6864,11 @@
         <v>4457</v>
       </c>
       <c r="B150" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445707000011/march200710-k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445706000008/march200610-k.htm</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -6881,7 +6881,7 @@
         <v>0</v>
       </c>
       <c r="G150" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -6907,11 +6907,11 @@
         <v>4457</v>
       </c>
       <c r="B151" t="n">
-        <v>2000</v>
+        <v>2007</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445700000067/0000004457-00-000067.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445707000011/march200710-k.htm</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -6924,7 +6924,7 @@
         <v>0</v>
       </c>
       <c r="G151" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -6939,7 +6939,7 @@
         <v>0</v>
       </c>
       <c r="L151" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M151" t="n">
         <v>0</v>
@@ -6950,11 +6950,11 @@
         <v>4457</v>
       </c>
       <c r="B152" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445709000006/body10-k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445710000021/body10-k.htm</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -6967,7 +6967,7 @@
         <v>0</v>
       </c>
       <c r="G152" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -7036,11 +7036,11 @@
         <v>4457</v>
       </c>
       <c r="B154" t="n">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445710000021/body10-k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445712000023/mar10k.htm</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -7053,7 +7053,7 @@
         <v>0</v>
       </c>
       <c r="G154" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -7079,11 +7079,11 @@
         <v>4457</v>
       </c>
       <c r="B155" t="n">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445711000059/mar10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445713000016/March201310KReport.htm</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -7096,7 +7096,7 @@
         <v>0</v>
       </c>
       <c r="G155" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -7122,11 +7122,11 @@
         <v>4457</v>
       </c>
       <c r="B156" t="n">
-        <v>2013</v>
+        <v>2009</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445713000016/March201310KReport.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445709000006/body10-k.htm</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -7165,11 +7165,11 @@
         <v>4457</v>
       </c>
       <c r="B157" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445712000023/mar10k.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445711000059/mar10k.htm</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -7208,11 +7208,11 @@
         <v>4457</v>
       </c>
       <c r="B158" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445714000036/March201410KReport.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445715000019/Mar201510K.htm</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -7225,7 +7225,7 @@
         <v>0</v>
       </c>
       <c r="G158" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -7251,11 +7251,11 @@
         <v>4457</v>
       </c>
       <c r="B159" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445715000019/Mar201510K.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445714000036/March201410KReport.htm</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -7268,7 +7268,7 @@
         <v>0</v>
       </c>
       <c r="G159" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -7294,11 +7294,11 @@
         <v>4457</v>
       </c>
       <c r="B160" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445718000016/March201810K.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445717000032/march201710K.htm</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -7380,11 +7380,11 @@
         <v>4457</v>
       </c>
       <c r="B162" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445717000032/march201710K.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445718000016/March201810K.htm</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -7466,11 +7466,11 @@
         <v>4457</v>
       </c>
       <c r="B164" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445721000040/uhal-20210331.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445720000053/uhal-20200331.htm</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -7483,7 +7483,7 @@
         <v>0</v>
       </c>
       <c r="G164" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
@@ -7509,11 +7509,11 @@
         <v>4457</v>
       </c>
       <c r="B165" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445720000053/uhal-20200331.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/0000004457/000000445721000040/uhal-20210331.htm</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -7526,7 +7526,7 @@
         <v>0</v>
       </c>
       <c r="G165" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
